--- a/JAMS/1차리뷰/제약요인 면적계산_WM_250703.xlsx
+++ b/JAMS/1차리뷰/제약요인 면적계산_WM_250703.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\카카오톡 받은 파일\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\Github\Raster_PV_Poten\JAMS\1차리뷰\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F8E5E11-C1FB-4EF9-9311-3F0E1F9461BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E13C8D5-BA37-49E1-8A0D-4CC1023DB821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7CFC9312-A0FB-4855-809E-90A752333824}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{7CFC9312-A0FB-4855-809E-90A752333824}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
   <si>
     <t>경사도 20도</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -154,18 +154,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>5110.408472503526 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>면적(km2)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1557.242762182821 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>UQM110</t>
   </si>
   <si>
@@ -214,7 +206,7 @@
     <t>시도지정문화재구역</t>
   </si>
   <si>
-    <t>803.1967910401536 </t>
+    <t>습지</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -223,10 +215,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="0.00000000000_);[Red]\(0.00000000000\)"/>
-    <numFmt numFmtId="177" formatCode="0.000000000000_);[Red]\(0.000000000000\)"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="189" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -254,6 +246,14 @@
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -290,23 +290,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -315,23 +312,39 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="189" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="189" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -664,348 +677,358 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5081A08B-B946-4AC4-B759-0DFB178C3D66}">
-  <dimension ref="A4:H30"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A4:H31"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="13.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.08203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A4" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="9"/>
+      <c r="B5" s="5"/>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
+      <c r="D5" s="7">
+        <v>5110.40847250352</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
       <c r="C6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="7">
+        <v>1557.2427621828199</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="7">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="8">
+        <v>31811.893635444099</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="7">
+        <v>274.22600004593801</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="9">
+        <v>1367.5956454828299</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A11" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="10">
+        <v>346.62807283147998</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="1" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A12" s="5"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="10">
+        <v>96.4202226055598</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A13" s="5"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="13">
+        <v>0.40568045779599998</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A14" s="5"/>
+      <c r="B14" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="9">
+        <v>22.260954798564999</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A15" s="5"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="11">
+        <v>58.730264022101302</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A16" s="5"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="11">
+        <v>12.7471753012415</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A17" s="5"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="14">
+        <v>7.7254413908637298E-2</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="12">
+        <v>2953.31</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="12"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="12"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="12"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="12"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="12"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="12"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="12"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A26" s="5"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26" s="12"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A27" s="5"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27" s="12"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A28" s="5"/>
+      <c r="B28" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="7">
+        <v>729.24050854411303</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A29" s="5"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" s="7">
+        <v>803.19679104015302</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A30" s="5"/>
+      <c r="B30" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30" s="7">
         <v>0</v>
       </c>
-      <c r="D7" s="3">
-        <v>31811.893635444099</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="2">
-        <v>274.22600004593801</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="1">
-        <v>1367.5956454828299</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="7">
-        <v>346.62807283147998</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="9"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="7">
-        <v>96.4202226055598</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="9"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="7">
-        <v>0.40568045779599998</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="9"/>
-      <c r="B13" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="1">
-        <v>22.260954798564999</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="9"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="8">
-        <v>58.730264022101302</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="9"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="8">
-        <v>12.7471753012415</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="9"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="8">
-        <v>7.7254413908637298E-2</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="10">
-        <v>2953.31</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18" s="10"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="10"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" s="10"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="10"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D22" s="10"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="10"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D24" s="10"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D25" s="10"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D26" s="10"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D27" s="2">
-        <v>729.24050854411303</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D29" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="1" t="s">
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D31" s="7">
         <v>1004.09529572334</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="A5:B9"/>
-    <mergeCell ref="A10:A30"/>
-    <mergeCell ref="D17:D26"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="A5:B10"/>
+    <mergeCell ref="A11:A31"/>
+    <mergeCell ref="D18:D27"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="B17:B26"/>
-    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="B18:B27"/>
+    <mergeCell ref="B28:B29"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
